--- a/research/traditional_assets/database/data/united_states/united_states_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_reinsurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10415</v>
+        <v>0.0563</v>
       </c>
       <c r="E2">
-        <v>0.009899999999999999</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="G2">
-        <v>0.04808271577159531</v>
+        <v>0.05855190247506465</v>
       </c>
       <c r="H2">
-        <v>0.04808271577159531</v>
+        <v>0.05855190247506465</v>
       </c>
       <c r="I2">
-        <v>0.07286815697454023</v>
+        <v>0.04641194632415979</v>
       </c>
       <c r="J2">
-        <v>0.05613436014163995</v>
+        <v>0.04340306811837958</v>
       </c>
       <c r="K2">
-        <v>1270.8</v>
+        <v>575</v>
       </c>
       <c r="L2">
-        <v>0.04611934123522025</v>
+        <v>0.03540204408324098</v>
       </c>
       <c r="M2">
-        <v>512.9</v>
+        <v>306</v>
       </c>
       <c r="N2">
-        <v>0.03099674259226803</v>
+        <v>0.032221719123485</v>
       </c>
       <c r="O2">
-        <v>0.4036040289581366</v>
+        <v>0.5321739130434783</v>
       </c>
       <c r="P2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="Q2">
-        <v>0.0116638161830917</v>
+        <v>0.02116524687523034</v>
       </c>
       <c r="R2">
-        <v>0.1518728360088133</v>
+        <v>0.3495652173913044</v>
       </c>
       <c r="S2">
-        <v>319.9</v>
+        <v>105</v>
       </c>
       <c r="T2">
-        <v>0.6237083252095925</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="U2">
-        <v>4022.5</v>
+        <v>3512</v>
       </c>
       <c r="V2">
-        <v>0.2430968942823127</v>
+        <v>0.3698126717701938</v>
       </c>
       <c r="W2">
-        <v>0.06186180258687737</v>
+        <v>0.0446255335661622</v>
       </c>
       <c r="X2">
-        <v>0.08947040976470769</v>
+        <v>0.1253685605656694</v>
       </c>
       <c r="Y2">
-        <v>-0.02760860717783032</v>
+        <v>-0.08074302699950722</v>
       </c>
       <c r="Z2">
-        <v>1.191641200396224</v>
+        <v>1.210203275314655</v>
       </c>
       <c r="AA2">
-        <v>0.07102093439496392</v>
+        <v>0.05252653519556803</v>
       </c>
       <c r="AB2">
-        <v>0.06945622032524908</v>
+        <v>0.09742839878843688</v>
       </c>
       <c r="AC2">
-        <v>0.001564714069714836</v>
+        <v>-0.04490186359286886</v>
       </c>
       <c r="AD2">
-        <v>6039.2</v>
+        <v>4207</v>
       </c>
       <c r="AE2">
-        <v>389.2354091466697</v>
+        <v>75.88583901498353</v>
       </c>
       <c r="AF2">
-        <v>6428.43540914667</v>
+        <v>4282.885839014984</v>
       </c>
       <c r="AG2">
-        <v>2405.93540914667</v>
+        <v>770.8858390149835</v>
       </c>
       <c r="AH2">
-        <v>0.279797238850644</v>
+        <v>0.3108138291710181</v>
       </c>
       <c r="AI2">
-        <v>0.2260712845310915</v>
+        <v>0.5336340342888084</v>
       </c>
       <c r="AJ2">
-        <v>0.1269432967262282</v>
+        <v>0.07507956116478283</v>
       </c>
       <c r="AK2">
-        <v>0.09855166405942527</v>
+        <v>0.1707809781877881</v>
       </c>
       <c r="AL2">
-        <v>270.7</v>
+        <v>128</v>
       </c>
       <c r="AM2">
-        <v>270.7</v>
+        <v>128</v>
       </c>
       <c r="AN2">
-        <v>2.383643826965582</v>
+        <v>4.947665529813007</v>
       </c>
       <c r="AO2">
-        <v>7.473956409309199</v>
+        <v>5.8984375</v>
       </c>
       <c r="AP2">
-        <v>0.9496113866224623</v>
+        <v>0.9066045384158339</v>
       </c>
       <c r="AQ2">
-        <v>7.473956409309199</v>
+        <v>5.8984375</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alleghany Corporation (NYSE:Y)</t>
+          <t>Reinsurance Group of America, Incorporated (NYSE:RGA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,255 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.13</v>
+        <v>0.0563</v>
       </c>
       <c r="E3">
-        <v>0.0452</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="G3">
-        <v>0.03702103918074977</v>
+        <v>0.05855190247506465</v>
       </c>
       <c r="H3">
-        <v>0.03702103918074977</v>
+        <v>0.05855190247506465</v>
       </c>
       <c r="I3">
-        <v>0.09207840583633678</v>
+        <v>0.04641194632415979</v>
       </c>
       <c r="J3">
-        <v>0.07386802329072188</v>
+        <v>0.04340306811837958</v>
       </c>
       <c r="K3">
-        <v>677.8</v>
+        <v>575</v>
       </c>
       <c r="L3">
-        <v>0.06099382682720515</v>
+        <v>0.03540204408324098</v>
       </c>
       <c r="M3">
-        <v>270.9</v>
+        <v>306</v>
       </c>
       <c r="N3">
-        <v>0.02962144903448728</v>
+        <v>0.032221719123485</v>
       </c>
       <c r="O3">
-        <v>0.3996754204780171</v>
+        <v>0.5321739130434783</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>201</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02116524687523034</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3495652173913044</v>
       </c>
       <c r="S3">
-        <v>270.9</v>
+        <v>105</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="U3">
-        <v>995.5</v>
+        <v>3512</v>
       </c>
       <c r="V3">
-        <v>0.1088525378878999</v>
+        <v>0.3698126717701938</v>
       </c>
       <c r="W3">
-        <v>0.07884695919222</v>
+        <v>0.0446255335661622</v>
       </c>
       <c r="X3">
-        <v>0.08590382397924455</v>
+        <v>0.1253685605656694</v>
       </c>
       <c r="Y3">
-        <v>-0.007056864787024553</v>
+        <v>-0.08074302699950722</v>
       </c>
       <c r="Z3">
-        <v>1.220849891241782</v>
+        <v>1.210203275314655</v>
       </c>
       <c r="AA3">
-        <v>0.09018176820072327</v>
+        <v>0.05252653519556803</v>
       </c>
       <c r="AB3">
-        <v>0.06950127288653521</v>
+        <v>0.09742839878843688</v>
       </c>
       <c r="AC3">
-        <v>0.02068049531418806</v>
+        <v>-0.04490186359286886</v>
       </c>
       <c r="AD3">
-        <v>2552.2</v>
+        <v>4207</v>
       </c>
       <c r="AE3">
-        <v>307.3475365156198</v>
+        <v>75.88583901498353</v>
       </c>
       <c r="AF3">
-        <v>2859.54753651562</v>
+        <v>4282.885839014984</v>
       </c>
       <c r="AG3">
-        <v>1864.04753651562</v>
+        <v>770.8858390149835</v>
       </c>
       <c r="AH3">
-        <v>0.2381974205066447</v>
+        <v>0.3108138291710181</v>
       </c>
       <c r="AI3">
-        <v>0.2386626208176119</v>
+        <v>0.5336340342888084</v>
       </c>
       <c r="AJ3">
-        <v>0.1693134492292219</v>
+        <v>0.07507956116478283</v>
       </c>
       <c r="AK3">
-        <v>0.1696740825415023</v>
+        <v>0.1707809781877881</v>
       </c>
       <c r="AL3">
-        <v>97.7</v>
+        <v>128</v>
       </c>
       <c r="AM3">
-        <v>97.7</v>
+        <v>128</v>
       </c>
       <c r="AN3">
-        <v>2.022345483359747</v>
+        <v>4.947665529813007</v>
       </c>
       <c r="AO3">
-        <v>10.60593654042989</v>
+        <v>5.8984375</v>
       </c>
       <c r="AP3">
-        <v>1.477058269822203</v>
+        <v>0.9066045384158339</v>
       </c>
       <c r="AQ3">
-        <v>10.60593654042989</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Reinsurance Group of America, Incorporated (NYSE:RGA)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Reinsurance</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.07829999999999999</v>
-      </c>
-      <c r="E4">
-        <v>-0.0254</v>
-      </c>
-      <c r="G4">
-        <v>0.05555893443619998</v>
-      </c>
-      <c r="H4">
-        <v>0.05555893443619998</v>
-      </c>
-      <c r="I4">
-        <v>0.0598845897989168</v>
-      </c>
-      <c r="J4">
-        <v>0.04422361363730718</v>
-      </c>
-      <c r="K4">
-        <v>593</v>
-      </c>
-      <c r="L4">
-        <v>0.03606617199854032</v>
-      </c>
-      <c r="M4">
-        <v>242</v>
-      </c>
-      <c r="N4">
-        <v>0.03269607511990813</v>
-      </c>
-      <c r="O4">
-        <v>0.4080944350758853</v>
-      </c>
-      <c r="P4">
-        <v>193</v>
-      </c>
-      <c r="Q4">
-        <v>0.02607579544686888</v>
-      </c>
-      <c r="R4">
-        <v>0.3254637436762226</v>
-      </c>
-      <c r="S4">
-        <v>49</v>
-      </c>
-      <c r="T4">
-        <v>0.2024793388429752</v>
-      </c>
-      <c r="U4">
-        <v>3027</v>
-      </c>
-      <c r="V4">
-        <v>0.4089711544957103</v>
-      </c>
-      <c r="W4">
-        <v>0.04487664598153474</v>
-      </c>
-      <c r="X4">
-        <v>0.09303699555017081</v>
-      </c>
-      <c r="Y4">
-        <v>-0.04816034956863607</v>
-      </c>
-      <c r="Z4">
-        <v>1.172678945111243</v>
-      </c>
-      <c r="AA4">
-        <v>0.05186010058920456</v>
-      </c>
-      <c r="AB4">
-        <v>0.06941116776396294</v>
-      </c>
-      <c r="AC4">
-        <v>-0.01755106717475838</v>
-      </c>
-      <c r="AD4">
-        <v>3487</v>
-      </c>
-      <c r="AE4">
-        <v>81.88787263104989</v>
-      </c>
-      <c r="AF4">
-        <v>3568.88787263105</v>
-      </c>
-      <c r="AG4">
-        <v>541.88787263105</v>
-      </c>
-      <c r="AH4">
-        <v>0.3253201175807758</v>
-      </c>
-      <c r="AI4">
-        <v>0.2169024063040712</v>
-      </c>
-      <c r="AJ4">
-        <v>0.0682187350435354</v>
-      </c>
-      <c r="AK4">
-        <v>0.04035841199922562</v>
-      </c>
-      <c r="AL4">
-        <v>173</v>
-      </c>
-      <c r="AM4">
-        <v>173</v>
-      </c>
-      <c r="AN4">
-        <v>2.742214532871972</v>
-      </c>
-      <c r="AO4">
-        <v>5.705202312138728</v>
-      </c>
-      <c r="AP4">
-        <v>0.4261464868127163</v>
-      </c>
-      <c r="AQ4">
-        <v>5.705202312138728</v>
+        <v>5.8984375</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_reinsurance.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0563</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.06280000000000001</v>
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
       </c>
       <c r="G2">
-        <v>0.05855190247506465</v>
+        <v>0.05822375752172944</v>
       </c>
       <c r="H2">
-        <v>0.05855190247506465</v>
+        <v>0.05822375752172944</v>
       </c>
       <c r="I2">
-        <v>0.04641194632415979</v>
+        <v>0.09655325505093537</v>
       </c>
       <c r="J2">
-        <v>0.04340306811837958</v>
+        <v>0.07439136697884148</v>
       </c>
       <c r="K2">
-        <v>575</v>
+        <v>1141</v>
       </c>
       <c r="L2">
-        <v>0.03540204408324098</v>
+        <v>0.06357254290171607</v>
       </c>
       <c r="M2">
-        <v>306</v>
+        <v>412</v>
       </c>
       <c r="N2">
-        <v>0.032221719123485</v>
+        <v>0.03864118099454146</v>
       </c>
       <c r="O2">
-        <v>0.5321739130434783</v>
+        <v>0.3610867659947414</v>
       </c>
       <c r="P2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="Q2">
-        <v>0.02116524687523034</v>
+        <v>0.02025848323985669</v>
       </c>
       <c r="R2">
-        <v>0.3495652173913044</v>
+        <v>0.189307624890447</v>
       </c>
       <c r="S2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="T2">
-        <v>0.3431372549019608</v>
+        <v>0.4757281553398058</v>
       </c>
       <c r="U2">
-        <v>3512</v>
+        <v>2820</v>
       </c>
       <c r="V2">
-        <v>0.3698126717701938</v>
+        <v>0.2644857534092401</v>
       </c>
       <c r="W2">
-        <v>0.0446255335661622</v>
+        <v>0.3123460169723515</v>
       </c>
       <c r="X2">
-        <v>0.1253685605656694</v>
+        <v>0.1037536173854589</v>
       </c>
       <c r="Y2">
-        <v>-0.08074302699950722</v>
+        <v>0.2085923995868926</v>
       </c>
       <c r="Z2">
-        <v>1.210203275314655</v>
+        <v>4.048441545907466</v>
       </c>
       <c r="AA2">
-        <v>0.05252653519556803</v>
+        <v>0.3011691007339907</v>
       </c>
       <c r="AB2">
-        <v>0.09742839878843688</v>
+        <v>0.08287244106169957</v>
       </c>
       <c r="AC2">
-        <v>-0.04490186359286886</v>
+        <v>0.2182966596722911</v>
       </c>
       <c r="AD2">
-        <v>4207</v>
+        <v>4450</v>
       </c>
       <c r="AE2">
-        <v>75.88583901498353</v>
+        <v>85.31089172905897</v>
       </c>
       <c r="AF2">
-        <v>4282.885839014984</v>
+        <v>4535.310891729059</v>
       </c>
       <c r="AG2">
-        <v>770.8858390149835</v>
+        <v>1715.310891729059</v>
       </c>
       <c r="AH2">
-        <v>0.3108138291710181</v>
+        <v>0.2984245857127374</v>
       </c>
       <c r="AI2">
-        <v>0.5336340342888084</v>
+        <v>0.357440082484535</v>
       </c>
       <c r="AJ2">
-        <v>0.07507956116478283</v>
+        <v>0.1385828626396338</v>
       </c>
       <c r="AK2">
-        <v>0.1707809781877881</v>
+        <v>0.1738201107108122</v>
       </c>
       <c r="AL2">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="AM2">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="AN2">
-        <v>4.947665529813007</v>
+        <v>2.618417181523978</v>
       </c>
       <c r="AO2">
-        <v>5.8984375</v>
+        <v>7.343220338983051</v>
       </c>
       <c r="AP2">
-        <v>0.9066045384158339</v>
+        <v>1.009303260799682</v>
       </c>
       <c r="AQ2">
-        <v>5.8984375</v>
+        <v>7.343220338983051</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0563</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.06280000000000001</v>
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.17</v>
       </c>
       <c r="G3">
-        <v>0.05855190247506465</v>
+        <v>0.05822375752172944</v>
       </c>
       <c r="H3">
-        <v>0.05855190247506465</v>
+        <v>0.05822375752172944</v>
       </c>
       <c r="I3">
-        <v>0.04641194632415979</v>
+        <v>0.09655325505093537</v>
       </c>
       <c r="J3">
-        <v>0.04340306811837958</v>
+        <v>0.07439136697884148</v>
       </c>
       <c r="K3">
-        <v>575</v>
+        <v>1141</v>
       </c>
       <c r="L3">
-        <v>0.03540204408324098</v>
+        <v>0.06357254290171607</v>
       </c>
       <c r="M3">
-        <v>306</v>
+        <v>412</v>
       </c>
       <c r="N3">
-        <v>0.032221719123485</v>
+        <v>0.03864118099454146</v>
       </c>
       <c r="O3">
-        <v>0.5321739130434783</v>
+        <v>0.3610867659947414</v>
       </c>
       <c r="P3">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="Q3">
-        <v>0.02116524687523034</v>
+        <v>0.02025848323985669</v>
       </c>
       <c r="R3">
-        <v>0.3495652173913044</v>
+        <v>0.189307624890447</v>
       </c>
       <c r="S3">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="T3">
-        <v>0.3431372549019608</v>
+        <v>0.4757281553398058</v>
       </c>
       <c r="U3">
-        <v>3512</v>
+        <v>2820</v>
       </c>
       <c r="V3">
-        <v>0.3698126717701938</v>
+        <v>0.2644857534092401</v>
       </c>
       <c r="W3">
-        <v>0.0446255335661622</v>
+        <v>0.3123460169723515</v>
       </c>
       <c r="X3">
-        <v>0.1253685605656694</v>
+        <v>0.1037536173854589</v>
       </c>
       <c r="Y3">
-        <v>-0.08074302699950722</v>
+        <v>0.2085923995868926</v>
       </c>
       <c r="Z3">
-        <v>1.210203275314655</v>
+        <v>4.048441545907466</v>
       </c>
       <c r="AA3">
-        <v>0.05252653519556803</v>
+        <v>0.3011691007339907</v>
       </c>
       <c r="AB3">
-        <v>0.09742839878843688</v>
+        <v>0.08287244106169957</v>
       </c>
       <c r="AC3">
-        <v>-0.04490186359286886</v>
+        <v>0.2182966596722911</v>
       </c>
       <c r="AD3">
-        <v>4207</v>
+        <v>4450</v>
       </c>
       <c r="AE3">
-        <v>75.88583901498353</v>
+        <v>85.31089172905897</v>
       </c>
       <c r="AF3">
-        <v>4282.885839014984</v>
+        <v>4535.310891729059</v>
       </c>
       <c r="AG3">
-        <v>770.8858390149835</v>
+        <v>1715.310891729059</v>
       </c>
       <c r="AH3">
-        <v>0.3108138291710181</v>
+        <v>0.2984245857127374</v>
       </c>
       <c r="AI3">
-        <v>0.5336340342888084</v>
+        <v>0.357440082484535</v>
       </c>
       <c r="AJ3">
-        <v>0.07507956116478283</v>
+        <v>0.1385828626396338</v>
       </c>
       <c r="AK3">
-        <v>0.1707809781877881</v>
+        <v>0.1738201107108122</v>
       </c>
       <c r="AL3">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="AM3">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="AN3">
-        <v>4.947665529813007</v>
+        <v>2.618417181523978</v>
       </c>
       <c r="AO3">
-        <v>5.8984375</v>
+        <v>7.343220338983051</v>
       </c>
       <c r="AP3">
-        <v>0.9066045384158339</v>
+        <v>1.009303260799682</v>
       </c>
       <c r="AQ3">
-        <v>5.8984375</v>
+        <v>7.343220338983051</v>
       </c>
     </row>
   </sheetData>
